--- a/dcf/DASH.xlsx
+++ b/dcf/DASH.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>129.5085195899576</v>
+        <v>109.6657281371058</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>124.7409269019511</v>
+        <v>105.7145139909586</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>120.1889359981943</v>
+        <v>101.9410331350337</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>115.8416618603472</v>
+        <v>98.33633565924586</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>111.6888202067939</v>
+        <v>94.89196488408551</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>107.7206916763769</v>
+        <v>91.59992797944625</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>103.9280883005939</v>
+        <v>88.45266845969547</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>138.3826428834209</v>
+        <v>116.9288059953688</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>133.2237473885</v>
+        <v>112.6573277894616</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>128.2993499473263</v>
+        <v>108.5790486355259</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>123.5975744378085</v>
+        <v>104.684207448843</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>119.1072015437359</v>
+        <v>100.9635822653972</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>114.8176295373957</v>
+        <v>97.40845807703943</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>110.7188375707404</v>
+        <v>94.0105967230257</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>147.2567661768841</v>
+        <v>124.1918838536318</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>141.706567875049</v>
+        <v>119.6001415879646</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>136.4097638964584</v>
+        <v>115.2170641360182</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>131.3534870152697</v>
+        <v>111.0320792384401</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>126.5255828806779</v>
+        <v>107.035199646709</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>121.9145673984145</v>
+        <v>103.2169881746326</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>117.5095868408869</v>
+        <v>99.56852498635594</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>156.1308894703474</v>
+        <v>131.4549617118948</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>150.189388361598</v>
+        <v>126.5429553864676</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>144.5201778455904</v>
+        <v>121.8550796365104</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>139.1093995927309</v>
+        <v>117.3799510280373</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>133.94396421762</v>
+        <v>113.1068170280208</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>129.0115052594334</v>
+        <v>109.0255182722258</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>124.3003361110334</v>
+        <v>105.1264532496862</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>165.0050127638106</v>
+        <v>138.7180395701578</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>158.6722088481469</v>
+        <v>133.4857691849706</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>152.6305917947224</v>
+        <v>128.4930951370027</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>146.8653121701922</v>
+        <v>123.7278228176344</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>141.362345554562</v>
+        <v>119.1784344093326</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>136.1084431204522</v>
+        <v>114.834048369819</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>131.0910853811799</v>
+        <v>110.6843815130164</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>173.8791360572738</v>
+        <v>145.9811174284208</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>167.1550293346959</v>
+        <v>140.4285829834736</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>160.7410057438545</v>
+        <v>135.1311106374949</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>154.6212247476534</v>
+        <v>130.0756946072315</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>148.780726891504</v>
+        <v>125.2500517906443</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>143.205380981471</v>
+        <v>120.6425784674122</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>137.8818346513264</v>
+        <v>116.2423097763467</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>182.7532593507371</v>
+        <v>153.2441952866838</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>175.6378498212448</v>
+        <v>147.3713967819766</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>168.8514196929866</v>
+        <v>141.7691261379872</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>162.3771373251146</v>
+        <v>136.4235663968286</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>156.199108228446</v>
+        <v>131.3216691719561</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>150.3023188424898</v>
+        <v>126.4511085650054</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>144.6725839214729</v>
+        <v>121.8002380396769</v>
       </c>
     </row>
     <row r="13">
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.9423507971740047</v>
+        <v>0.945694676263121</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24414,7 +24414,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>139.1093995927309</v>
+        <v>117.3799510280373</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>196.7454384441001</v>
+        <v>161.9007980422153</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>96.51772194883979</v>
+        <v>83.56860529160204</v>
       </c>
     </row>
     <row r="59">
